--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487777_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487777_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4731</v>
+        <v>7.0676</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5854</v>
+        <v>6.1212</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8877</v>
+        <v>0.9464</v>
       </c>
       <c r="G2" t="n">
         <v>2.841</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3242</v>
+        <v>0.2703</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0867</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.411</v>
+        <v>-0.3522</v>
       </c>
       <c r="V2" t="n">
         <v>1.8751</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1087</v>
+        <v>3.7569</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1964</v>
+        <v>3.726</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9123</v>
+        <v>0.0309</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4905</v>
+        <v>1.1298</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.1405</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5716</v>
+        <v>1.2703</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9476</v>
+        <v>1.8116</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1639</v>
+        <v>0.1535</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.6581</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.6818</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.245</v>
+        <v>-0.294</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7879</v>
+        <v>-0.3878</v>
       </c>
       <c r="P3" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>2.742</v>
+        <v>0.9621</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4132</v>
+        <v>0.7468</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3289</v>
+        <v>0.2153</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1238</v>
+        <v>1.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4648</v>
+        <v>3.0582</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4045</v>
+        <v>2.987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0603</v>
+        <v>0.0711</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1298</v>
+        <v>1.3408</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1405</v>
+        <v>1.2535</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2703</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8116</v>
+        <v>2.9657</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1535</v>
+        <v>1.8864</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6581</v>
+        <v>1.0793</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6818</v>
+        <v>-1.6249</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.294</v>
+        <v>-0.6329</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3878</v>
+        <v>-0.9919</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>0.67</v>
+        <v>-0.2796</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4253</v>
+        <v>0.2482</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2447</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2725</v>
+        <v>2.8125</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2013</v>
+        <v>1.0177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0711</v>
+        <v>1.7948</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3408</v>
+        <v>1.4905</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2535</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08740000000000001</v>
+        <v>1.5716</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9657</v>
+        <v>0.9476</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8864</v>
+        <v>0.1639</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0793</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6249</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6329</v>
+        <v>-0.245</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9919</v>
+        <v>0.7879</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8731</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9137</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.4459</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4625</v>
+        <v>1.2345</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5276999999999999</v>
+        <v>0.2114</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1238</v>
+        <v>-0.1238</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8137</v>
+        <v>-0.1238</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2788</v>
+        <v>1.1786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.208</v>
+        <v>0.5683</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0708</v>
+        <v>0.6102</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2209</v>
+        <v>0.448</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8316</v>
+        <v>0.4431</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6107</v>
+        <v>0.0049</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3106</v>
+        <v>0.5258</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3498</v>
+        <v>0.8842</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>-0.3584</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0897</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4818</v>
+        <v>-0.4411</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5715</v>
+        <v>0.3633</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2081</v>
+        <v>2.4974</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2916</v>
+        <v>-0.2694</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.3725</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.227</v>
+        <v>-0.6419</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0016</v>
+        <v>0.3669</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2889</v>
+        <v>0.208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2873</v>
+        <v>0.1589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.448</v>
+        <v>-0.2209</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4431</v>
+        <v>-0.8316</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0049</v>
+        <v>0.6107</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5258</v>
+        <v>-0.3106</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8842</v>
+        <v>-0.3498</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3584</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07770000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4411</v>
+        <v>-0.4818</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3633</v>
+        <v>0.5715</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4974</v>
+        <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4496</v>
+        <v>0.3797</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4848</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9649</v>
+        <v>-0.139</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7335</v>
+        <v>-0.7923</v>
       </c>
       <c r="E8" t="n">
         <v>-0.3413</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3922</v>
+        <v>-0.4509</v>
       </c>
       <c r="G8" t="n">
         <v>0.4581</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3373</v>
+        <v>-0.396</v>
       </c>
       <c r="T8" t="n">
         <v>-0.261</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.135</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3622</v>
+        <v>-0.8749</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.38</v>
+        <v>-0.9513</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0177</v>
+        <v>0.0765</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8669</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.871</v>
+        <v>-0.3836</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2838</v>
+        <v>-0.225</v>
       </c>
       <c r="V9" t="n">
         <v>1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.693</v>
+        <v>-2.312</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5855</v>
+        <v>-1.4096</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8925</v>
+        <v>-0.9024</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6206</v>
+        <v>-2.0713</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0747</v>
+        <v>0.1045</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4541</v>
+        <v>-2.1758</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2286</v>
+        <v>-1.0834</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6826</v>
+        <v>0.3454</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9112</v>
+        <v>-1.4287</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8492</v>
+        <v>-0.9879</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3921</v>
+        <v>-0.2409</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4572</v>
+        <v>-0.747</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3299</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4053</v>
+        <v>-0.657</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8259</v>
+        <v>-0.3262</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5794</v>
+        <v>-0.3308</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6452</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7907</v>
+        <v>-2.3471</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1382</v>
+        <v>-0.4597</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6525</v>
+        <v>-1.8874</v>
       </c>
       <c r="G11" t="n">
         <v>-1.408</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>0.533</v>
+        <v>-0.0233</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4253</v>
+        <v>0.1039</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1077</v>
+        <v>-0.1272</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7076</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3707</v>
+        <v>-2.3667</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4096</v>
+        <v>-3.907</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9612000000000001</v>
+        <v>1.5402</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0713</v>
+        <v>-0.6206</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1045</v>
+        <v>-2.0747</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1758</v>
+        <v>1.4541</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0834</v>
+        <v>0.2286</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3454</v>
+        <v>-1.6826</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4287</v>
+        <v>1.9112</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9879</v>
+        <v>-0.8492</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2409</v>
+        <v>-0.3921</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.747</v>
+        <v>-0.4572</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4162</v>
+        <v>3.3299</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7157</v>
+        <v>0.7315</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3262</v>
+        <v>0.5044</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3895</v>
+        <v>0.2271</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.6452</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3042</v>
+        <v>-3.2059</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1936</v>
+        <v>-5.3007</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8893</v>
+        <v>2.0948</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3567</v>
@@ -1468,13 +1468,13 @@
         <v>3.1218</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4502</v>
+        <v>-0.3518</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1643</v>
+        <v>0.0572</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6145</v>
+        <v>-0.409</v>
       </c>
       <c r="V13" t="n">
         <v>0.5838</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.342000000000001</v>
+        <v>6.341800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.258500000000002</v>
+        <v>2.258600000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>4.083100000000002</v>
+        <v>4.0831</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1638000000000006</v>
+        <v>0.1637999999999993</v>
       </c>
       <c r="H14" t="n">
         <v>1.2252</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.061400000000001</v>
+        <v>-1.0614</v>
       </c>
       <c r="J14" t="n">
         <v>8.962200000000003</v>
@@ -1525,7 +1525,7 @@
         <v>5.615099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.347300000000001</v>
+        <v>3.3473</v>
       </c>
       <c r="M14" t="n">
         <v>-8.798399999999999</v>
@@ -1546,10 +1546,10 @@
         <v>20.8118</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4287</v>
+        <v>1.4288</v>
       </c>
       <c r="T14" t="n">
-        <v>3.662599999999999</v>
+        <v>3.6628</v>
       </c>
       <c r="U14" t="n">
         <v>-2.234</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1746</v>
+        <v>6.0818</v>
       </c>
       <c r="E15" t="n">
-        <v>5.033</v>
+        <v>5.2473</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1416</v>
+        <v>0.8344</v>
       </c>
       <c r="G15" t="n">
         <v>4.0577</v>
@@ -1624,13 +1624,13 @@
         <v>2.7055</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9049</v>
+        <v>0.0023</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1239</v>
+        <v>0.3382</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0288</v>
+        <v>-0.3359</v>
       </c>
       <c r="V15" t="n">
         <v>1.3975</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1992</v>
+        <v>2.0173</v>
       </c>
       <c r="E16" t="n">
-        <v>1.318</v>
+        <v>1.7458</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8812</v>
+        <v>0.2716</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.226</v>
+        <v>2.1552</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4285</v>
+        <v>-0.1724</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2025</v>
+        <v>2.3276</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4217</v>
+        <v>3.0739</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6568000000000001</v>
+        <v>1.0362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2351</v>
+        <v>2.0378</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8043</v>
+        <v>-0.9187</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.2086</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0326</v>
+        <v>0.2898</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.4974</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.1396</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.1675</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.6649</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.8841</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.6336</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.2506</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.1238</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1061</v>
-      </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.961</v>
+        <v>1.3929</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4958</v>
+        <v>0.4608</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.9321</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1552</v>
+        <v>-1.226</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1724</v>
+        <v>-1.4285</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3276</v>
+        <v>0.2025</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0739</v>
+        <v>-0.4217</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0362</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0378</v>
+        <v>0.2351</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9187</v>
+        <v>-0.8043</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2086</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2898</v>
+        <v>-0.0326</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4974</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5571</v>
+        <v>1.0778</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5031</v>
+        <v>0.7763</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9459</v>
+        <v>0.3014</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1675</v>
+        <v>-0.1238</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0941</v>
+        <v>0.0528</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5561</v>
+        <v>-0.3011</v>
       </c>
       <c r="F18" t="n">
-        <v>0.538</v>
+        <v>0.354</v>
       </c>
       <c r="G18" t="n">
         <v>1.3366</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2122</v>
+        <v>0.171</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0992</v>
+        <v>0.242</v>
       </c>
       <c r="U18" t="n">
-        <v>0.113</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>1.8751</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8669</v>
+        <v>0.0016</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2282</v>
+        <v>-1.8683</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6387</v>
+        <v>1.8699</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0509</v>
+        <v>2.0248</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4582</v>
+        <v>0.9317</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5927</v>
+        <v>1.0932</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1943</v>
+        <v>2.6782</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07679999999999999</v>
+        <v>1.234</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1176</v>
+        <v>1.4442</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2452</v>
+        <v>-0.6534</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5349</v>
+        <v>-0.3023</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7103</v>
+        <v>-0.351</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-6.2435</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>2.9137</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6485</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6524</v>
+        <v>0.0696</v>
       </c>
       <c r="U19" t="n">
-        <v>0.004</v>
+        <v>-0.1604</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="X19" t="n">
         <v>-0.23</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9794</v>
+        <v>-0.2572</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1897</v>
+        <v>0.4148</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2103</v>
+        <v>-0.672</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0248</v>
+        <v>-1.0509</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9317</v>
+        <v>-0.4582</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0932</v>
+        <v>-0.5927</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6782</v>
+        <v>0.1943</v>
       </c>
       <c r="K20" t="n">
-        <v>1.234</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4442</v>
+        <v>0.1176</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6534</v>
+        <v>-1.2452</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3023</v>
+        <v>-0.5349</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.351</v>
+        <v>-0.7103</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.3299</v>
+        <v>0.8325</v>
       </c>
       <c r="Q20" t="n">
-        <v>-6.2435</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0719</v>
+        <v>-0.0388</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2519</v>
+        <v>-0.0095</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.82</v>
+        <v>-0.0293</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
         <v>-0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4896</v>
+        <v>-1.0125</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3222</v>
+        <v>-2.7864</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8326</v>
+        <v>1.7739</v>
       </c>
       <c r="G21" t="n">
         <v>0.1334</v>
@@ -2092,13 +2092,13 @@
         <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0013</v>
+        <v>0.4784</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.0262</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5109</v>
+        <v>0.4522</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5838</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7586</v>
+        <v>-4.6182</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6773</v>
+        <v>-4.9988</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.3807</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0056</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4169</v>
+        <v>-0.2765</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3849</v>
+        <v>0.0634</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8018</v>
+        <v>-0.3398</v>
       </c>
       <c r="V22" t="n">
         <v>0.2477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.676299999999999</v>
+        <v>-7.1428</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0688</v>
+        <v>-1.9973</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.6074</v>
+        <v>-5.1455</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5891</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0414</v>
+        <v>-0.5079</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0967</v>
+        <v>-0.0252</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9446</v>
+        <v>-0.4827</v>
       </c>
       <c r="V23" t="n">
         <v>-4.6701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.341900000000001</v>
+        <v>-3.4843</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.083299999999999</v>
+        <v>-4.0832</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2584</v>
+        <v>0.5991</v>
       </c>
       <c r="G24" t="n">
         <v>-0.1639000000000013</v>
@@ -2326,13 +2326,13 @@
         <v>17.69</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4289</v>
+        <v>1.4289</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2341</v>
+        <v>2.234</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.6626</v>
+        <v>-0.8050999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6274</v>
